--- a/FINAL_SUBMISSION/11_AI使用记录/11_AI使用记录.xlsx
+++ b/FINAL_SUBMISSION/11_AI使用记录/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -515,6 +515,76 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 20:01:39</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-07收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>生成3条决策：买入沪深300ETF(510300)；买入紫金矿业(601899)；买入中国平安(601318)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:38:14</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-08收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：买入长江电力(600900)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FINAL_SUBMISSION/11_AI使用记录/11_AI使用记录.xlsx
+++ b/FINAL_SUBMISSION/11_AI使用记录/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -585,6 +585,41 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:46:35</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>人工主动减仓：卖出紫金矿业 18200 股 @ 33.860（部分止盈）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>已按人工指令登记决策记录与交易流水，并通过规则引擎校验</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>成交价与数量由操作人提供；行情数据来自东财/腾讯公开接口</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED——人工主动决策并已成交</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>写入决策记录（07）与交易账本（09）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
